--- a/doc/data/estimating service-2.xlsx
+++ b/doc/data/estimating service-2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinstenzig/dev/MartinStenzig/delta-samples/doc/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289A1AD2-3EE7-6B48-B14F-06E4C54BF86E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7109CE23-8A07-D14D-A8B5-26EEF7B6F947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18020" yWindow="4060" windowWidth="51200" windowHeight="28200" xr2:uid="{2B6504EB-1901-3B41-A24B-28BA69293AD5}"/>
+    <workbookView xWindow="340" yWindow="1720" windowWidth="34560" windowHeight="21680" xr2:uid="{2B6504EB-1901-3B41-A24B-28BA69293AD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -68,9 +68,6 @@
     <t>Cost Element / Value Category</t>
   </si>
   <si>
-    <t>xxxxxx / Material Cost</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -83,9 +80,6 @@
     <t>Labor Cost</t>
   </si>
   <si>
-    <t>xxxxxx / Internal Labor</t>
-  </si>
-  <si>
     <t>USD</t>
   </si>
   <si>
@@ -150,6 +144,12 @@
   </si>
   <si>
     <t>Plant</t>
+  </si>
+  <si>
+    <t>94311000 Pers Hours / Internal Labor</t>
+  </si>
+  <si>
+    <t>51700000 Consptn Repair Mat / Material Cost</t>
   </si>
 </sst>
 </file>
@@ -541,7 +541,7 @@
     <col min="9" max="9" width="37.5" customWidth="1"/>
     <col min="10" max="10" width="20.5" customWidth="1"/>
     <col min="11" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="40.33203125" customWidth="1"/>
     <col min="17" max="17" width="24.5" customWidth="1"/>
     <col min="19" max="19" width="19" customWidth="1"/>
   </cols>
@@ -551,22 +551,22 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
       </c>
       <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>35</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
       </c>
       <c r="I4" t="s">
         <v>3</v>
@@ -578,28 +578,28 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
       </c>
       <c r="N4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O4" t="s">
         <v>11</v>
       </c>
-      <c r="O4" t="s">
-        <v>12</v>
-      </c>
       <c r="Q4" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" t="s">
         <v>17</v>
       </c>
-      <c r="R4" t="s">
-        <v>19</v>
-      </c>
       <c r="S4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:20" x14ac:dyDescent="0.2">
@@ -607,7 +607,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
         <v>0</v>
@@ -619,25 +619,25 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N5" s="1">
         <v>180</v>
       </c>
       <c r="O5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q5" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>18</v>
       </c>
-      <c r="R5" t="s">
-        <v>20</v>
-      </c>
       <c r="S5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.2">
@@ -645,10 +645,10 @@
         <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" t="s">
         <v>0</v>
@@ -660,48 +660,48 @@
         <v>1</v>
       </c>
       <c r="M6" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="N6" s="1">
         <v>200</v>
       </c>
       <c r="O6" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>18</v>
-      </c>
-      <c r="R6" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q7" t="s">
         <v>29</v>
       </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>31</v>
-      </c>
       <c r="S7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.2">
       <c r="J8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.2">
       <c r="J9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.2">
       <c r="M10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
